--- a/passport.xlsx
+++ b/passport.xlsx
@@ -759,6 +759,11 @@
           <t>SAT 2026</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -776,6 +781,11 @@
           <t>SAT 2026</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -793,6 +803,11 @@
           <t>SAT 2026</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -810,6 +825,11 @@
           <t>SAT 2026</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -827,6 +847,11 @@
           <t>SAT 2026</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -842,6 +867,11 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>SAT 2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/passport.xlsx
+++ b/passport.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS7"/>
+  <dimension ref="A1:AS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -875,6 +875,94 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ffd4bb50</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SAT 2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>313563cf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Teymour</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SAT 2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>58925826</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jaiah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SAT 2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>f05749b9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Saad</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SAT 2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="H2:AS200">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">

--- a/passport.xlsx
+++ b/passport.xlsx
@@ -764,6 +764,9 @@
           <t>14/18</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -808,6 +811,9 @@
           <t>12/18</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -830,6 +836,9 @@
           <t>15/18</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -852,6 +861,9 @@
           <t>14/18</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -874,6 +886,9 @@
           <t>14/18</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -896,6 +911,9 @@
           <t>13/18</t>
         </is>
       </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -918,6 +936,9 @@
           <t>9/18</t>
         </is>
       </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -940,6 +961,9 @@
           <t>11/18</t>
         </is>
       </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -961,6 +985,9 @@
         <is>
           <t>14/18</t>
         </is>
+      </c>
+      <c r="H11" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/passport.xlsx
+++ b/passport.xlsx
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
